--- a/data/varios/DimSucursal.xlsx
+++ b/data/varios/DimSucursal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir\Documents\Reportes\track\TRACK BI\data\varios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9463A630-C005-4361-8F74-5DDD14E36281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4272C17-DCF7-4166-81E5-55C1B713209C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28908" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{AA51AAD3-CDFC-4F7D-B42C-F33914DE8F7E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA51AAD3-CDFC-4F7D-B42C-F33914DE8F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Sucursal</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>TLALNEPANTLA</t>
+  </si>
+  <si>
+    <t>SALTILLO VILLALTA</t>
   </si>
 </sst>
 </file>
@@ -466,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAC510E-E346-4BAC-8C2B-E3F1DB97245B}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
@@ -681,6 +684,14 @@
         <v>1336</v>
       </c>
     </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
